--- a/data/Excel_view/anomaly_top20.xlsx
+++ b/data/Excel_view/anomaly_top20.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,120 +699,130 @@
       </c>
       <c r="BE1" t="inlineStr">
         <is>
+          <t>is_charging</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>is_discharging</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
           <t>cell_voltage_spread_V</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>comp_cell_voltage_spread_V</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>temp_mean_C</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>temp_std_C</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>temp_max_C</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>temp_min_C</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>temp_spread_C</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>dT_mean_C</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>dT_max_C</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>dT_spread_C</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>dT_mean_dt_Cps</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>dT_max_dt_Cps</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>dT_spread_dt_Cps</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>temp_spread_per_current</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>temp_mean_per_current</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>volt_spread_per_current</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>I_mean_120s</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>V_mean_120s</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>T_mean_120s</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>T_std_120s</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>T_spread_120s</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>Vspread_mean_120s</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>anomaly</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>anomaly_score</t>
         </is>
@@ -821,26 +831,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02 12:29:13</t>
+          <t>2026-03-02 12:41:17</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>1.57</v>
       </c>
       <c r="E2" t="n">
-        <v>444.99</v>
+        <v>451.31</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.33</v>
+        <v>709</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
         <v>21</v>
@@ -852,112 +862,112 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="L2" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="M2" t="n">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="P2" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="R2" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>24</v>
+      </c>
+      <c r="U2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AP2" t="n">
         <v>24.7</v>
       </c>
-      <c r="S2" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AQ2" t="n">
         <v>23.4</v>
       </c>
-      <c r="AH2" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>23</v>
-      </c>
       <c r="AR2" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -968,307 +978,313 @@
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>2.4649</v>
       </c>
       <c r="AY2" t="n">
-        <v>-16.54</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-2.939999999999998</v>
+        <v>-0.2400000000000091</v>
       </c>
       <c r="BA2" t="n">
-        <v>-16.54</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-2.939999999999998</v>
+        <v>-0.2400000000000091</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.33</v>
+        <v>709</v>
       </c>
       <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF2" t="n">
-        <v>0.0300000000000002</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>23.384375</v>
-      </c>
       <c r="BH2" t="n">
-        <v>0.9500795807075422</v>
+        <v>0.04</v>
       </c>
       <c r="BI2" t="n">
-        <v>24.7</v>
+        <v>23.803125</v>
       </c>
       <c r="BJ2" t="n">
-        <v>21</v>
+        <v>0.9576464345197484</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.699999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0031250000000007</v>
+        <v>21.3</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0031250000000007</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>3700000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>23384375</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>30000.00000000025</v>
+        <v>2.420382165605096</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.45322033898305</v>
+        <v>15.16122611464968</v>
       </c>
       <c r="BV2" t="n">
-        <v>447.5102542372881</v>
+        <v>0.0191082802547772</v>
       </c>
       <c r="BW2" t="n">
-        <v>23.35092690677966</v>
+        <v>17.06806722689075</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9603228801421592</v>
+        <v>453.8375630252101</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.787288135593221</v>
+        <v>23.76176470588236</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0122033898305084</v>
+        <v>0.9563436449247292</v>
       </c>
       <c r="CA2" t="n">
+        <v>3.789075630252101</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.0152100840336133</v>
+      </c>
+      <c r="CC2" t="n">
         <v>-1</v>
       </c>
-      <c r="CB2" t="n">
-        <v>-0.1041591799869087</v>
+      <c r="CD2" t="n">
+        <v>-0.0942730924089565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02 11:59:13</t>
+          <t>2026-03-02 12:41:16</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>94</v>
       </c>
       <c r="C3" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="E3" t="n">
-        <v>434.13</v>
+        <v>451.55</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>709.39</v>
       </c>
       <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>23</v>
       </c>
-      <c r="H3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="O3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>21</v>
-      </c>
-      <c r="X3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>21.1</v>
-      </c>
       <c r="AK3" t="n">
-        <v>22.4</v>
+        <v>24.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>23.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.3</v>
+        <v>23.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>22.8</v>
+        <v>24.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.7</v>
+        <v>24.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21.5</v>
+        <v>23.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>21.8</v>
+        <v>23.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>23.3</v>
+        <v>25.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>23.2</v>
+        <v>25</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_100856.csv</t>
+          <t>hvbDatalog_2026-03-02_120814.csv</t>
         </is>
       </c>
       <c r="AV3" t="n">
         <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>2.4649</v>
       </c>
       <c r="AY3" t="n">
-        <v>-16.9</v>
+        <v>-14.87</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-3.009999999999991</v>
+        <v>-2.620000000000005</v>
       </c>
       <c r="BA3" t="n">
-        <v>-16.9</v>
+        <v>-14.87</v>
       </c>
       <c r="BB3" t="n">
-        <v>-3.009999999999991</v>
+        <v>-2.620000000000005</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>709.39</v>
       </c>
       <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF3" t="n">
-        <v>0.0300000000000002</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>21.853125</v>
-      </c>
       <c r="BH3" t="n">
-        <v>0.9270084994564592</v>
+        <v>0.04</v>
       </c>
       <c r="BI3" t="n">
-        <v>23.3</v>
+        <v>23.803125</v>
       </c>
       <c r="BJ3" t="n">
-        <v>19.7</v>
+        <v>0.9576464345197484</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.600000000000001</v>
+        <v>25.1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0031250000000007</v>
+        <v>21.3</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0031250000000007</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
         <v>0</v>
@@ -1277,62 +1293,68 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>3600000.000000001</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>21853125</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>30000.00000000025</v>
+        <v>2.420382165605096</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.77576271186441</v>
+        <v>15.16122611464968</v>
       </c>
       <c r="BV3" t="n">
-        <v>436.7144915254237</v>
+        <v>0.0191082802547772</v>
       </c>
       <c r="BW3" t="n">
-        <v>21.77420550847458</v>
+        <v>17.20075630252101</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.9126370156106514</v>
+        <v>453.853949579832</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.517796610169491</v>
+        <v>23.76110819327731</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0117796610169493</v>
+        <v>0.956271181332051</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.789075630252102</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0.0151260504201679</v>
+      </c>
+      <c r="CC3" t="n">
         <v>-1</v>
       </c>
-      <c r="CB3" t="n">
-        <v>-0.0948418875750726</v>
+      <c r="CD3" t="n">
+        <v>-0.0942730924089565</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02 12:23:13</t>
+          <t>2026-03-02 12:05:16</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>94</v>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="E4" t="n">
-        <v>442.73</v>
+        <v>436.54</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.33</v>
+        <v>689.73</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
         <v>20</v>
@@ -1344,174 +1366,174 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="L4" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="O4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AL4" t="n">
         <v>23</v>
       </c>
-      <c r="P4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>23</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="AM4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AO4" t="n">
         <v>23.3</v>
       </c>
-      <c r="U4" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AP4" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AT4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AA4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>24.4</v>
-      </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_120814.csv</t>
+          <t>hvbDatalog_2026-03-02_100856.csv</t>
         </is>
       </c>
       <c r="AV4" t="n">
         <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>2.4964</v>
       </c>
       <c r="AY4" t="n">
-        <v>-17.09</v>
+        <v>-13.84</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-3</v>
+        <v>-2.479999999999961</v>
       </c>
       <c r="BA4" t="n">
-        <v>-17.09</v>
+        <v>-13.84</v>
       </c>
       <c r="BB4" t="n">
-        <v>-3</v>
+        <v>-2.479999999999961</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.33</v>
+        <v>689.73</v>
       </c>
       <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1</v>
       </c>
-      <c r="BE4" t="n">
-        <v>0.04</v>
-      </c>
       <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BG4" t="n">
-        <v>23.16875</v>
-      </c>
       <c r="BH4" t="n">
-        <v>0.9680167620516202</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="BI4" t="n">
-        <v>24.5</v>
+        <v>22.27812500000001</v>
       </c>
       <c r="BJ4" t="n">
-        <v>20.7</v>
+        <v>0.9417671703907536</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.800000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -1520,46 +1542,52 @@
         <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="BR4" t="n">
-        <v>3800000.000000001</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>23168750</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>40000.00000000004</v>
+        <v>2.341772151898734</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.85974789915966</v>
+        <v>14.10007911392405</v>
       </c>
       <c r="BV4" t="n">
-        <v>445.305294117647</v>
+        <v>0.018987341772152</v>
       </c>
       <c r="BW4" t="n">
-        <v>23.12423844537816</v>
+        <v>16.69966386554622</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.9615593447738556</v>
+        <v>439.0368067226891</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.787394957983194</v>
+        <v>22.20869222689076</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0125210084033613</v>
+        <v>0.9449143816803096</v>
       </c>
       <c r="CA4" t="n">
+        <v>3.717647058823531</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.0105882352941178</v>
+      </c>
+      <c r="CC4" t="n">
         <v>-1</v>
       </c>
-      <c r="CB4" t="n">
-        <v>-0.09264473558662301</v>
+      <c r="CD4" t="n">
+        <v>-0.0836791206948317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02 12:41:13</t>
+          <t>2026-03-02 12:41:14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1569,13 +1597,13 @@
         <v>94</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>17.64</v>
       </c>
       <c r="E5" t="n">
-        <v>451.26</v>
+        <v>454.29</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.35</v>
+        <v>8012.77</v>
       </c>
       <c r="G5" t="n">
         <v>25</v>
@@ -1590,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="M5" t="n">
         <v>4.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="O5" t="n">
         <v>23.6</v>
@@ -1656,7 +1684,7 @@
         <v>21.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AH5" t="n">
         <v>23.8</v>
@@ -1706,128 +1734,134 @@
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>17.64</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>311.1696</v>
       </c>
       <c r="AY5" t="n">
-        <v>-17.36</v>
+        <v>17.64</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-3.189999999999998</v>
+        <v>3.03000000000003</v>
       </c>
       <c r="BA5" t="n">
-        <v>-17.36</v>
+        <v>17.64</v>
       </c>
       <c r="BB5" t="n">
-        <v>-3.189999999999998</v>
+        <v>3.03000000000003</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.35</v>
+        <v>8012.77</v>
       </c>
       <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF5" t="n">
-        <v>0.0199999999999995</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>23.80625</v>
-      </c>
       <c r="BH5" t="n">
-        <v>0.957462203414705</v>
+        <v>0.0299999999999993</v>
       </c>
       <c r="BI5" t="n">
+        <v>23.803125</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.9576464345197484</v>
+      </c>
+      <c r="BK5" t="n">
         <v>25.1</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BL5" t="n">
         <v>21.3</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BM5" t="n">
         <v>3.800000000000001</v>
       </c>
-      <c r="BL5" t="n">
-        <v>0.0031249999999971</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0.0031250000000007</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0031249999999971</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
         <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0.0031250000000007</v>
       </c>
       <c r="BR5" t="n">
-        <v>3800000.000000001</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>23806250</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>30000.00000000025</v>
+        <v>0.2154195011337868</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.3381512605042</v>
+        <v>1.34938350340136</v>
       </c>
       <c r="BV5" t="n">
-        <v>453.8510924369748</v>
+        <v>0.0017006802721088</v>
       </c>
       <c r="BW5" t="n">
-        <v>23.75908613445377</v>
+        <v>17.34067226890756</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.9561888074138338</v>
+        <v>453.8601680672269</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.789075630252101</v>
+        <v>23.75976890756302</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0149579831932771</v>
+        <v>0.9561937625766032</v>
       </c>
       <c r="CA5" t="n">
+        <v>3.789075630252102</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.0150420168067225</v>
+      </c>
+      <c r="CC5" t="n">
         <v>-1</v>
       </c>
-      <c r="CB5" t="n">
-        <v>-0.0912760251142217</v>
+      <c r="CD5" t="n">
+        <v>-0.0808907337912064</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02 12:47:13</t>
+          <t>2026-03-02 21:33:26</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>94</v>
       </c>
       <c r="C6" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-13.64</v>
       </c>
       <c r="E6" t="n">
-        <v>452.97</v>
+        <v>395.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-5397.31</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1836,244 +1870,250 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="L6" t="n">
-        <v>4.02</v>
+        <v>3.51</v>
       </c>
       <c r="M6" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="N6" t="n">
-        <v>4.02</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>23.6</v>
+        <v>17.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>17.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.1</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>25.1</v>
+        <v>17.9</v>
       </c>
       <c r="S6" t="n">
-        <v>23.7</v>
+        <v>17.1</v>
       </c>
       <c r="T6" t="n">
-        <v>24</v>
+        <v>17.2</v>
       </c>
       <c r="U6" t="n">
-        <v>24.9</v>
+        <v>17.5</v>
       </c>
       <c r="V6" t="n">
-        <v>24.9</v>
+        <v>17.5</v>
       </c>
       <c r="W6" t="n">
-        <v>23.2</v>
+        <v>16.4</v>
       </c>
       <c r="X6" t="n">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>24.5</v>
+        <v>16.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.7</v>
+        <v>16.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>22.9</v>
+        <v>16.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.8</v>
+        <v>16.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>23.7</v>
+        <v>16.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>21.3</v>
+        <v>16.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>21.6</v>
+        <v>16.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>23.7</v>
+        <v>16.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>23.8</v>
+        <v>16.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>22.8</v>
+        <v>16.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.1</v>
+        <v>16.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>24.4</v>
+        <v>16.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>24.5</v>
+        <v>16.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>23.1</v>
+        <v>16.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.4</v>
+        <v>16.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>24.8</v>
+        <v>17.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.7</v>
+        <v>17.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23.5</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>23.8</v>
+        <v>17.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>25.2</v>
+        <v>17.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_120814.csv</t>
+          <t>hvbDatalog_2026-03-02_200953.csv</t>
         </is>
       </c>
       <c r="AV6" t="n">
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>186.0496</v>
       </c>
       <c r="AY6" t="n">
-        <v>-9.609999999999999</v>
+        <v>-0.0099999999999997</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.769999999999982</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-9.609999999999999</v>
+        <v>-0.0099999999999997</v>
       </c>
       <c r="BB6" t="n">
-        <v>-1.769999999999982</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>5397.31</v>
       </c>
       <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
         <v>1</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BG6" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF6" t="n">
-        <v>0.0200000000000004</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>23.834375</v>
-      </c>
       <c r="BH6" t="n">
-        <v>0.9607152493442476</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BI6" t="n">
-        <v>25.2</v>
+        <v>16.984375</v>
       </c>
       <c r="BJ6" t="n">
-        <v>21.3</v>
+        <v>0.5747983517384944</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.899999999999999</v>
+        <v>18</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0031250000000007</v>
+        <v>16.1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.899999999999998</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>0.009374999999998501</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.0031250000000007</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>0.009374999999998501</v>
       </c>
       <c r="BR6" t="n">
-        <v>3899999.999999999</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BS6" t="n">
-        <v>23834375</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BT6" t="n">
-        <v>30000.00000000025</v>
+        <v>0.1392961876832843</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.05330508474576</v>
+        <v>1.245188782991203</v>
       </c>
       <c r="BV6" t="n">
-        <v>454.7872033898305</v>
+        <v>0.002199413489736</v>
       </c>
       <c r="BW6" t="n">
-        <v>23.84385593220339</v>
+        <v>-13.61245762711864</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.9613541415895068</v>
+        <v>396.2022033898305</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.887288135593219</v>
+        <v>16.92235169491525</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0101694915254235</v>
+        <v>0.5644755061473349</v>
       </c>
       <c r="CA6" t="n">
+        <v>1.822033898305082</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.0229661016949153</v>
+      </c>
+      <c r="CC6" t="n">
         <v>-1</v>
       </c>
-      <c r="CB6" t="n">
-        <v>-0.08843560140717729</v>
+      <c r="CD6" t="n">
+        <v>-0.0802273818002775</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02 12:35:13</t>
+          <t>2026-03-02 12:05:14</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16.94</v>
       </c>
       <c r="E7" t="n">
-        <v>447.71</v>
+        <v>439.23</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>7438.78</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2082,420 +2122,426 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.02</v>
+        <v>3.91</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="M7" t="n">
-        <v>4.02</v>
+        <v>3.89</v>
       </c>
       <c r="N7" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>23.4</v>
+        <v>22.2</v>
       </c>
       <c r="P7" t="n">
-        <v>23.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.8</v>
+        <v>23.6</v>
       </c>
       <c r="R7" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="S7" t="n">
-        <v>23.5</v>
+        <v>21.9</v>
       </c>
       <c r="T7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AS7" t="n">
         <v>23.7</v>
       </c>
-      <c r="U7" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X7" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AT7" t="n">
         <v>23.6</v>
       </c>
-      <c r="AD7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>24.8</v>
-      </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_120814.csv</t>
+          <t>hvbDatalog_2026-03-02_100856.csv</t>
         </is>
       </c>
       <c r="AV7" t="n">
         <v>1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>16.94</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>286.9636</v>
       </c>
       <c r="AY7" t="n">
-        <v>-17.05</v>
+        <v>16.94</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-3.160000000000025</v>
+        <v>2.920000000000016</v>
       </c>
       <c r="BA7" t="n">
-        <v>-17.05</v>
+        <v>16.94</v>
       </c>
       <c r="BB7" t="n">
-        <v>-3.160000000000025</v>
+        <v>2.920000000000016</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>7438.78</v>
       </c>
       <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1</v>
       </c>
-      <c r="BE7" t="n">
-        <v>0.0199999999999995</v>
-      </c>
       <c r="BF7" t="n">
-        <v>0.0499999999999993</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>23.584375</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.953807099926902</v>
+        <v>0.04</v>
       </c>
       <c r="BI7" t="n">
-        <v>24.9</v>
+        <v>22.278125</v>
       </c>
       <c r="BJ7" t="n">
-        <v>21.1</v>
+        <v>0.9427941912722918</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.799999999999997</v>
+        <v>23.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0031249999999971</v>
+        <v>20</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>0.0062500000000014</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0031249999999971</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
         <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>0.0062500000000014</v>
       </c>
       <c r="BR7" t="n">
-        <v>3799999.999999997</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>23584375</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>19999.99999999957</v>
+        <v>0.2184179456906729</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.9746218487395</v>
+        <v>1.315119539551358</v>
       </c>
       <c r="BV7" t="n">
-        <v>450.3442857142857</v>
+        <v>0.0017709563164108</v>
       </c>
       <c r="BW7" t="n">
-        <v>23.53933823529412</v>
+        <v>16.84403361344538</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.9536163042699232</v>
+        <v>439.0526050420168</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.765546218487394</v>
+        <v>22.20638130252101</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0120168067226888</v>
+        <v>0.9449179796347296</v>
       </c>
       <c r="CA7" t="n">
+        <v>3.717647058823531</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.0103361344537817</v>
+      </c>
+      <c r="CC7" t="n">
         <v>-1</v>
       </c>
-      <c r="CB7" t="n">
-        <v>-0.0881588588057223</v>
+      <c r="CD7" t="n">
+        <v>-0.08009665787060941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02 12:05:13</t>
+          <t>2026-03-02 12:29:16</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>1.56</v>
       </c>
       <c r="E8" t="n">
-        <v>436.31</v>
+        <v>445.27</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.31</v>
+        <v>694.17</v>
       </c>
       <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="O8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>23</v>
       </c>
-      <c r="H8" t="n">
-        <v>19</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="O8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="AO8" t="n">
+      <c r="AR8" t="n">
         <v>23.3</v>
       </c>
-      <c r="AP8" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>22.2</v>
-      </c>
       <c r="AS8" t="n">
-        <v>23.7</v>
+        <v>24.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_100856.csv</t>
+          <t>hvbDatalog_2026-03-02_120814.csv</t>
         </is>
       </c>
       <c r="AV8" t="n">
         <v>1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>2.4336</v>
       </c>
       <c r="AY8" t="n">
-        <v>-16.93</v>
+        <v>-14.85</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-3.120000000000005</v>
+        <v>-2.54000000000002</v>
       </c>
       <c r="BA8" t="n">
-        <v>-16.93</v>
+        <v>-14.85</v>
       </c>
       <c r="BB8" t="n">
-        <v>-3.120000000000005</v>
+        <v>-2.54000000000002</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.31</v>
+        <v>694.17</v>
       </c>
       <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF8" t="n">
-        <v>0.0500000000000002</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>22.271875</v>
-      </c>
       <c r="BH8" t="n">
-        <v>0.943990970090765</v>
+        <v>0.02</v>
       </c>
       <c r="BI8" t="n">
-        <v>23.7</v>
+        <v>23.390625</v>
       </c>
       <c r="BJ8" t="n">
-        <v>20</v>
+        <v>0.9592871597382659</v>
       </c>
       <c r="BK8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BM8" t="n">
         <v>3.699999999999999</v>
       </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -2504,314 +2550,326 @@
         <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BR8" t="n">
-        <v>3700000</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>22271875</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>30000.00000000025</v>
+        <v>2.371794871794872</v>
       </c>
       <c r="BU8" t="n">
-        <v>16.8455462184874</v>
+        <v>14.99399038461538</v>
       </c>
       <c r="BV8" t="n">
-        <v>439.0483193277311</v>
+        <v>0.0192307692307693</v>
       </c>
       <c r="BW8" t="n">
-        <v>22.20522584033614</v>
+        <v>16.32720338983051</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.9449154633981516</v>
+        <v>447.5054237288136</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.717647058823532</v>
+        <v>23.35296610169491</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0101680672268909</v>
+        <v>0.9603915680074656</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.784745762711866</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.0126271186440677</v>
+      </c>
+      <c r="CC8" t="n">
         <v>-1</v>
       </c>
-      <c r="CB8" t="n">
-        <v>-0.086642998575689</v>
+      <c r="CD8" t="n">
+        <v>-0.078786467951192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02 12:37:14</t>
+          <t>2026-03-02 11:41:15</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
-        <v>16.99</v>
+        <v>2.56</v>
       </c>
       <c r="E9" t="n">
-        <v>451.96</v>
+        <v>426.12</v>
       </c>
       <c r="F9" t="n">
-        <v>7678.42</v>
+        <v>1090.44</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="O9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U9" t="n">
         <v>21</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="O9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>24.7</v>
-      </c>
       <c r="V9" t="n">
-        <v>24.7</v>
+        <v>21</v>
       </c>
       <c r="W9" t="n">
-        <v>22.9</v>
+        <v>19.6</v>
       </c>
       <c r="X9" t="n">
-        <v>23.2</v>
+        <v>19.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>24.3</v>
+        <v>20.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>24.1</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.7</v>
+        <v>19.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.7</v>
+        <v>20.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>23.5</v>
+        <v>20.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>21.1</v>
+        <v>18.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.4</v>
+        <v>18.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>23.6</v>
+        <v>20.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>23.7</v>
+        <v>20.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22.9</v>
+        <v>19.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>24.2</v>
+        <v>20.7</v>
       </c>
       <c r="AL9" t="n">
-        <v>24.3</v>
+        <v>20.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>22.9</v>
+        <v>19.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.2</v>
+        <v>19.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>24.7</v>
+        <v>21</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.6</v>
+        <v>20.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23.2</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>23.6</v>
+        <v>20.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>21.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>24.8</v>
+        <v>21.6</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_120814.csv</t>
+          <t>hvbDatalog_2026-03-02_100856.csv</t>
         </is>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.99</v>
+        <v>2.56</v>
       </c>
       <c r="AX9" t="n">
-        <v>288.6600999999999</v>
+        <v>6.5536</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.0400000000000027</v>
+        <v>-13.22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-2.319999999999993</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.0400000000000027</v>
+        <v>-13.22</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-2.319999999999993</v>
       </c>
       <c r="BC9" t="n">
-        <v>7678.42</v>
+        <v>1090.44</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0200000000000004</v>
+        <v>1</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>23.64375</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.9701803955966128</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BI9" t="n">
-        <v>25</v>
+        <v>20.296875</v>
       </c>
       <c r="BJ9" t="n">
-        <v>21.1</v>
+        <v>0.7912767857159106</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.899999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0093750000000021</v>
+        <v>18.6</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1000000000000014</v>
+        <v>3</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0093750000000021</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.2295467787200247</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.391627345990151</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001177162967795</v>
+        <v>1.171875</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.93084745762712</v>
+        <v>7.928466796875</v>
       </c>
       <c r="BV9" t="n">
-        <v>451.3819491525424</v>
+        <v>0.0117187499999999</v>
       </c>
       <c r="BW9" t="n">
-        <v>23.61358580508475</v>
+        <v>15.65033613445378</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.9574961421038064</v>
+        <v>428.2293277310925</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.795762711864404</v>
+        <v>20.20926995798319</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.014830508474576</v>
+        <v>0.775578299251263</v>
       </c>
       <c r="CA9" t="n">
+        <v>3.001680672268908</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.0151260504201681</v>
+      </c>
+      <c r="CC9" t="n">
         <v>-1</v>
       </c>
-      <c r="CB9" t="n">
-        <v>-0.0803606457336199</v>
+      <c r="CD9" t="n">
+        <v>-0.07829352673997431</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02 21:33:26</t>
+          <t>2026-03-02 12:37:14</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D10" t="n">
-        <v>-13.64</v>
+        <v>16.99</v>
       </c>
       <c r="E10" t="n">
-        <v>395.78</v>
+        <v>451.96</v>
       </c>
       <c r="F10" t="n">
-        <v>-5397.31</v>
+        <v>7678.42</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2820,244 +2878,250 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="L10" t="n">
-        <v>3.51</v>
+        <v>4.01</v>
       </c>
       <c r="M10" t="n">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.97</v>
       </c>
       <c r="O10" t="n">
-        <v>17.7</v>
+        <v>23.5</v>
       </c>
       <c r="P10" t="n">
-        <v>17.9</v>
+        <v>23.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>24.9</v>
       </c>
       <c r="R10" t="n">
-        <v>17.9</v>
+        <v>24.9</v>
       </c>
       <c r="S10" t="n">
-        <v>17.1</v>
+        <v>23.5</v>
       </c>
       <c r="T10" t="n">
-        <v>17.2</v>
+        <v>23.8</v>
       </c>
       <c r="U10" t="n">
-        <v>17.5</v>
+        <v>24.7</v>
       </c>
       <c r="V10" t="n">
-        <v>17.5</v>
+        <v>24.7</v>
       </c>
       <c r="W10" t="n">
-        <v>16.4</v>
+        <v>22.9</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>23.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.8</v>
+        <v>24.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.7</v>
+        <v>24.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.2</v>
+        <v>22.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.2</v>
+        <v>22.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.7</v>
+        <v>23.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.6</v>
+        <v>23.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.1</v>
+        <v>21.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.3</v>
+        <v>21.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.8</v>
+        <v>23.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.8</v>
+        <v>23.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>16.3</v>
+        <v>22.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.4</v>
+        <v>22.9</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.8</v>
+        <v>24.2</v>
       </c>
       <c r="AL10" t="n">
-        <v>16.9</v>
+        <v>24.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>16.7</v>
+        <v>22.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.8</v>
+        <v>23.2</v>
       </c>
       <c r="AO10" t="n">
-        <v>17.4</v>
+        <v>24.7</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.3</v>
+        <v>24.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>23.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>17.2</v>
+        <v>23.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.9</v>
+        <v>24.8</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_200953.csv</t>
+          <t>hvbDatalog_2026-03-02_120814.csv</t>
         </is>
       </c>
       <c r="AV10" t="n">
         <v>1</v>
       </c>
       <c r="AW10" t="n">
-        <v>13.64</v>
+        <v>16.99</v>
       </c>
       <c r="AX10" t="n">
-        <v>186.0496</v>
+        <v>288.6600999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.0099999999999997</v>
+        <v>-0.0400000000000027</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.0099999999999997</v>
+        <v>-0.0400000000000027</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>5397.31</v>
+        <v>7678.42</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0300000000000002</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0300000000000002</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>16.984375</v>
+        <v>0.0200000000000004</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.5747983517384944</v>
+        <v>0.02</v>
       </c>
       <c r="BI10" t="n">
-        <v>18</v>
+        <v>23.64375</v>
       </c>
       <c r="BJ10" t="n">
-        <v>16.1</v>
+        <v>0.9701803955966128</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.899999999999998</v>
+        <v>25</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.009374999999998501</v>
+        <v>21.1</v>
       </c>
       <c r="BM10" t="n">
+        <v>3.899999999999999</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.0093750000000021</v>
+      </c>
+      <c r="BO10" t="n">
         <v>0.1000000000000014</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0.009374999999998501</v>
       </c>
       <c r="BP10" t="n">
         <v>0.1000000000000014</v>
       </c>
       <c r="BQ10" t="n">
+        <v>0.0093750000000021</v>
+      </c>
+      <c r="BR10" t="n">
         <v>0.1000000000000014</v>
       </c>
-      <c r="BR10" t="n">
-        <v>0.1392961774709546</v>
-      </c>
       <c r="BS10" t="n">
-        <v>1.245188691701709</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0021994133284887</v>
+        <v>0.2295467922307238</v>
       </c>
       <c r="BU10" t="n">
-        <v>-13.61245762711864</v>
+        <v>1.391627427898764</v>
       </c>
       <c r="BV10" t="n">
-        <v>396.2022033898305</v>
+        <v>0.0011771630370806</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.92235169491525</v>
+        <v>16.93084745762712</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.5644755061473349</v>
+        <v>451.3819491525424</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.822033898305082</v>
+        <v>23.61358580508475</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0229661016949153</v>
+        <v>0.9574961421038064</v>
       </c>
       <c r="CA10" t="n">
+        <v>3.795762711864404</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.014830508474576</v>
+      </c>
+      <c r="CC10" t="n">
         <v>-1</v>
       </c>
-      <c r="CB10" t="n">
-        <v>-0.07656157077900549</v>
+      <c r="CD10" t="n">
+        <v>-0.0774107923302001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02 12:05:14</t>
+          <t>2026-03-02 11:59:16</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>94</v>
       </c>
       <c r="C11" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>16.94</v>
+        <v>4.59</v>
       </c>
       <c r="E11" t="n">
-        <v>439.23</v>
+        <v>434.78</v>
       </c>
       <c r="F11" t="n">
-        <v>7438.78</v>
+        <v>1994.75</v>
       </c>
       <c r="G11" t="n">
         <v>23</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -3066,112 +3130,112 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="L11" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.88</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.89</v>
       </c>
       <c r="N11" t="n">
         <v>3.85</v>
       </c>
       <c r="O11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="P11" t="n">
         <v>22.2</v>
       </c>
-      <c r="P11" t="n">
-        <v>22.6</v>
-      </c>
       <c r="Q11" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="R11" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="S11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>21</v>
+      </c>
+      <c r="X11" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG11" t="n">
         <v>21.9</v>
       </c>
-      <c r="T11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AH11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AT11" t="n">
         <v>23.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>23.6</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -3182,61 +3246,61 @@
         <v>1</v>
       </c>
       <c r="AW11" t="n">
-        <v>16.94</v>
+        <v>4.59</v>
       </c>
       <c r="AX11" t="n">
-        <v>286.9636</v>
+        <v>21.0681</v>
       </c>
       <c r="AY11" t="n">
-        <v>16.94</v>
+        <v>-9.25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.920000000000016</v>
+        <v>-1.630000000000052</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.94</v>
+        <v>-9.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.920000000000016</v>
+        <v>-1.630000000000052</v>
       </c>
       <c r="BC11" t="n">
-        <v>7438.78</v>
+        <v>1994.75</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
       </c>
       <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>22.278125</v>
-      </c>
       <c r="BH11" t="n">
-        <v>0.9427941912722918</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="BI11" t="n">
-        <v>23.7</v>
+        <v>21.859375</v>
       </c>
       <c r="BJ11" t="n">
-        <v>20</v>
+        <v>0.9224299518820016</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.699999999999999</v>
+        <v>23.3</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0062500000000014</v>
+        <v>19.7</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0062500000000014</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
         <v>0</v>
@@ -3245,65 +3309,71 @@
         <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.2184179327970523</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.315119461917387</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.001770956211868</v>
+        <v>0.7843137254901964</v>
       </c>
       <c r="BU11" t="n">
-        <v>16.84403361344538</v>
+        <v>4.762391067538125</v>
       </c>
       <c r="BV11" t="n">
-        <v>439.0526050420168</v>
+        <v>0.0065359477124183</v>
       </c>
       <c r="BW11" t="n">
-        <v>22.20638130252101</v>
+        <v>16.64432203389831</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.9449179796347296</v>
+        <v>436.7062711864406</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.717647058823531</v>
+        <v>21.77825741525424</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0103361344537817</v>
+        <v>0.9130884936835008</v>
       </c>
       <c r="CA11" t="n">
+        <v>3.520338983050847</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.011949152542373</v>
+      </c>
+      <c r="CC11" t="n">
         <v>-1</v>
       </c>
-      <c r="CB11" t="n">
-        <v>-0.0764854501586443</v>
+      <c r="CD11" t="n">
+        <v>-0.07001732550746451</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02 07:09:08</t>
+          <t>2026-03-02 12:35:14</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>94</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>17.63</v>
       </c>
       <c r="E12" t="n">
-        <v>349.04</v>
+        <v>450.78</v>
       </c>
       <c r="F12" t="n">
-        <v>1.05</v>
+        <v>7946.75</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3312,216 +3382,222 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.12</v>
+        <v>4.01</v>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>4.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="O12" t="n">
-        <v>14.9</v>
+        <v>23.4</v>
       </c>
       <c r="P12" t="n">
-        <v>15.1</v>
+        <v>23.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="R12" t="n">
-        <v>14.7</v>
+        <v>24.9</v>
       </c>
       <c r="S12" t="n">
-        <v>14.2</v>
+        <v>23.5</v>
       </c>
       <c r="T12" t="n">
-        <v>14.2</v>
+        <v>23.7</v>
       </c>
       <c r="U12" t="n">
-        <v>14.1</v>
+        <v>24.7</v>
       </c>
       <c r="V12" t="n">
-        <v>14.1</v>
+        <v>24.7</v>
       </c>
       <c r="W12" t="n">
-        <v>13.8</v>
+        <v>22.8</v>
       </c>
       <c r="X12" t="n">
-        <v>13.9</v>
+        <v>23.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.8</v>
+        <v>24.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.8</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.6</v>
+        <v>22.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>13.7</v>
+        <v>23.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.6</v>
+        <v>23.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>13.7</v>
+        <v>21.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.7</v>
+        <v>21.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.6</v>
+        <v>23.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>13.7</v>
+        <v>23.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>13.8</v>
+        <v>22.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>13.8</v>
+        <v>22.8</v>
       </c>
       <c r="AK12" t="n">
-        <v>13.8</v>
+        <v>24.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>13.9</v>
+        <v>24.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.1</v>
+        <v>22.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.1</v>
+        <v>23.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>14.2</v>
+        <v>24.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.1</v>
+        <v>24.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.4</v>
+        <v>23.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>23.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>14.8</v>
+        <v>24.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_060731.csv</t>
+          <t>hvbDatalog_2026-03-02_120814.csv</t>
         </is>
       </c>
       <c r="AV12" t="n">
         <v>1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>17.63</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>310.8169</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.01</v>
+        <v>17.63</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>3.069999999999993</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.01</v>
+        <v>17.63</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>3.069999999999993</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.05</v>
+        <v>7946.75</v>
       </c>
       <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1</v>
       </c>
-      <c r="BE12" t="n">
-        <v>0.02</v>
-      </c>
       <c r="BF12" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>14.090625</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.4402047727313777</v>
+        <v>0.0699999999999998</v>
       </c>
       <c r="BI12" t="n">
-        <v>15.1</v>
+        <v>23.584375</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13.6</v>
+        <v>0.953807099926902</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.5</v>
+        <v>24.9</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0093750000000003</v>
+        <v>21.1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0999999999999996</v>
+        <v>3.799999999999997</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0093750000000003</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>14090625</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>20000.00000000002</v>
+        <v>0.2155416903006237</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.009322033898305</v>
+        <v>1.337741066364152</v>
       </c>
       <c r="BV12" t="n">
-        <v>349.0402542372881</v>
+        <v>0.0017016449234259</v>
       </c>
       <c r="BW12" t="n">
-        <v>14.08355402542373</v>
+        <v>16.97756302521008</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.4270072967498288</v>
+        <v>450.3521848739496</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.405932203389831</v>
+        <v>23.54002100840336</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.02</v>
+        <v>0.953595371529928</v>
       </c>
       <c r="CA12" t="n">
+        <v>3.765546218487394</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.0121008403361342</v>
+      </c>
+      <c r="CC12" t="n">
         <v>-1</v>
       </c>
-      <c r="CB12" t="n">
-        <v>-0.0745571199498912</v>
+      <c r="CD12" t="n">
+        <v>-0.069620865345541</v>
       </c>
     </row>
     <row r="13">
@@ -3698,104 +3774,110 @@
         <v>0</v>
       </c>
       <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG13" t="n">
         <v>0.0299999999999998</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BH13" t="n">
         <v>0.0299999999999998</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BI13" t="n">
         <v>19.18125000000001</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BJ13" t="n">
         <v>0.6331882969187276</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BK13" t="n">
         <v>20.3</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>17.9</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BM13" t="n">
         <v>2.400000000000002</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BN13" t="n">
         <v>0.0062500000000014</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BO13" t="n">
         <v>0.1000000000000014</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.0062500000000014</v>
       </c>
       <c r="BP13" t="n">
         <v>0.1000000000000014</v>
       </c>
       <c r="BQ13" t="n">
+        <v>0.0062500000000014</v>
+      </c>
+      <c r="BR13" t="n">
         <v>0.1000000000000014</v>
       </c>
-      <c r="BR13" t="n">
-        <v>0.1991701079526883</v>
-      </c>
       <c r="BS13" t="n">
-        <v>1.591804847153125</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0024896263494085</v>
+        <v>0.1991701244813279</v>
       </c>
       <c r="BU13" t="n">
+        <v>1.591804979253112</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.0024896265560165</v>
+      </c>
+      <c r="BW13" t="n">
         <v>-12.07338983050848</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="BX13" t="n">
         <v>374.1602542372881</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="BY13" t="n">
         <v>19.12717161016949</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="BZ13" t="n">
         <v>0.6308883353534096</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CA13" t="n">
         <v>2.379661016949152</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CB13" t="n">
         <v>0.0219491525423729</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CC13" t="n">
         <v>-1</v>
       </c>
-      <c r="CB13" t="n">
-        <v>-0.0623476306292345</v>
+      <c r="CD13" t="n">
+        <v>-0.0695902300709397</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02 13:05:16</t>
+          <t>2026-03-02 11:53:14</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>94</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="E14" t="n">
-        <v>453.26</v>
+        <v>434.05</v>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>6630.95</v>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3804,238 +3886,244 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.04</v>
+        <v>3.87</v>
       </c>
       <c r="L14" t="n">
-        <v>4.03</v>
+        <v>3.83</v>
       </c>
       <c r="M14" t="n">
-        <v>4.04</v>
+        <v>3.86</v>
       </c>
       <c r="N14" t="n">
-        <v>4.03</v>
+        <v>3.82</v>
       </c>
       <c r="O14" t="n">
-        <v>23.1</v>
+        <v>21.4</v>
       </c>
       <c r="P14" t="n">
-        <v>23.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.4</v>
+        <v>22.7</v>
       </c>
       <c r="R14" t="n">
-        <v>24.4</v>
+        <v>22.7</v>
       </c>
       <c r="S14" t="n">
-        <v>23.2</v>
+        <v>21</v>
       </c>
       <c r="T14" t="n">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="U14" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="V14" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="W14" t="n">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
       <c r="X14" t="n">
-        <v>23.1</v>
+        <v>20.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>23.9</v>
+        <v>21.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
       <c r="AA14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AO14" t="n">
         <v>22.2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AM14" t="n">
+      <c r="AP14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AS14" t="n">
         <v>22.7</v>
       </c>
-      <c r="AN14" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>24.5</v>
-      </c>
       <c r="AT14" t="n">
-        <v>24.4</v>
+        <v>22.7</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_120814.csv</t>
+          <t>hvbDatalog_2026-03-02_100856.csv</t>
         </is>
       </c>
       <c r="AV14" t="n">
         <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>233.4784</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.01</v>
+        <v>-1.56</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0.1299999999999954</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.01</v>
+        <v>-1.56</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0.1299999999999954</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.36</v>
+        <v>6630.95</v>
       </c>
       <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1</v>
       </c>
-      <c r="BE14" t="n">
-        <v>0.0099999999999997</v>
-      </c>
       <c r="BF14" t="n">
-        <v>0.0099999999999997</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>23.234375</v>
+        <v>0.04</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.931044981762168</v>
+        <v>0.04</v>
       </c>
       <c r="BI14" t="n">
-        <v>24.5</v>
+        <v>21.353125</v>
       </c>
       <c r="BJ14" t="n">
-        <v>20.6</v>
+        <v>0.8893580051308484</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.899999999999999</v>
+        <v>22.7</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0062500000000014</v>
+        <v>19.3</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1000000000000014</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0062500000000014</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BR14" t="n">
-        <v>3899999.999999999</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>23234375</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>9999.999999999787</v>
+        <v>0.2225130890052355</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0060504201680672</v>
+        <v>1.39745582460733</v>
       </c>
       <c r="BV14" t="n">
-        <v>453.3004201680672</v>
+        <v>0.0026178010471204</v>
       </c>
       <c r="BW14" t="n">
-        <v>23.26811974789916</v>
+        <v>16.20932773109244</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.928681311143604</v>
+        <v>433.9155462184873</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.81764705882353</v>
+        <v>21.2671481092437</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0099999999999997</v>
+        <v>0.8806604987131451</v>
       </c>
       <c r="CA14" t="n">
+        <v>3.381512605042017</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.0156302521008403</v>
+      </c>
+      <c r="CC14" t="n">
         <v>-1</v>
       </c>
-      <c r="CB14" t="n">
-        <v>-0.0616658899818524</v>
+      <c r="CD14" t="n">
+        <v>-0.0657970841631296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02 12:41:14</t>
+          <t>2026-03-02 12:47:22</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>94</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>17.64</v>
+        <v>1.57</v>
       </c>
       <c r="E15" t="n">
-        <v>454.29</v>
+        <v>452.82</v>
       </c>
       <c r="F15" t="n">
-        <v>8012.77</v>
+        <v>712.74</v>
       </c>
       <c r="G15" t="n">
         <v>25</v>
@@ -4050,16 +4138,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="L15" t="n">
         <v>4.02</v>
       </c>
       <c r="M15" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="N15" t="n">
         <v>4.02</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.99</v>
       </c>
       <c r="O15" t="n">
         <v>23.6</v>
@@ -4068,7 +4156,7 @@
         <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="R15" t="n">
         <v>25.1</v>
@@ -4089,10 +4177,10 @@
         <v>23.1</v>
       </c>
       <c r="X15" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Z15" t="n">
         <v>24.3</v>
@@ -4104,7 +4192,7 @@
         <v>22.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AD15" t="n">
         <v>23.7</v>
@@ -4122,13 +4210,13 @@
         <v>23.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AL15" t="n">
         <v>24.5</v>
@@ -4146,10 +4234,10 @@
         <v>24.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AS15" t="n">
         <v>25.1</v>
@@ -4166,128 +4254,134 @@
         <v>1</v>
       </c>
       <c r="AW15" t="n">
-        <v>17.64</v>
+        <v>1.57</v>
       </c>
       <c r="AX15" t="n">
-        <v>311.1696</v>
+        <v>2.4649</v>
       </c>
       <c r="AY15" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.03000000000003</v>
+        <v>-0.0400000000000204</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.03000000000003</v>
+        <v>-0.0400000000000204</v>
       </c>
       <c r="BC15" t="n">
-        <v>8012.77</v>
+        <v>712.74</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0300000000000002</v>
+        <v>1</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0299999999999993</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>23.803125</v>
+        <v>0.0200000000000004</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.9576464345197484</v>
+        <v>0.0100000000000006</v>
       </c>
       <c r="BI15" t="n">
+        <v>23.825</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.9568092134630296</v>
+      </c>
+      <c r="BK15" t="n">
         <v>25.1</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>21.3</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BM15" t="n">
         <v>3.800000000000001</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BN15" t="n">
         <v>-0.0031250000000007</v>
       </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
       <c r="BO15" t="n">
+        <v>-0.0999999999999978</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.0999999999999978</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>-0.0031250000000007</v>
       </c>
-      <c r="BP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>0</v>
-      </c>
       <c r="BR15" t="n">
-        <v>0.2154194889217977</v>
+        <v>-0.0999999999999978</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.349383426905701</v>
+        <v>-0.0999999999999978</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0017006801756984</v>
+        <v>2.420382165605096</v>
       </c>
       <c r="BU15" t="n">
-        <v>17.34067226890756</v>
+        <v>15.17515923566879</v>
       </c>
       <c r="BV15" t="n">
-        <v>453.8601680672269</v>
+        <v>0.012738853503185</v>
       </c>
       <c r="BW15" t="n">
-        <v>23.75976890756302</v>
+        <v>10.40576271186441</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.9561937625766032</v>
+        <v>454.6790677966102</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.789075630252102</v>
+        <v>23.84277012711864</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0150420168067225</v>
+        <v>0.96090180807091</v>
       </c>
       <c r="CA15" t="n">
+        <v>3.886440677966101</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.0108474576271184</v>
+      </c>
+      <c r="CC15" t="n">
         <v>-1</v>
       </c>
-      <c r="CB15" t="n">
-        <v>-0.060866178312124</v>
+      <c r="CD15" t="n">
+        <v>-0.0654246862908195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02 11:47:15</t>
+          <t>2026-03-02 09:49:12</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>94</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>15.39</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>431.4</v>
+        <v>379.76</v>
       </c>
       <c r="F16" t="n">
-        <v>6640.6</v>
+        <v>3372.26</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -4296,244 +4390,250 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="L16" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>20.8</v>
+        <v>14.6</v>
       </c>
       <c r="P16" t="n">
-        <v>21.3</v>
+        <v>14.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.1</v>
+        <v>14.4</v>
       </c>
       <c r="R16" t="n">
-        <v>22.1</v>
+        <v>14.3</v>
       </c>
       <c r="S16" t="n">
-        <v>20.5</v>
+        <v>13.9</v>
       </c>
       <c r="T16" t="n">
-        <v>20.7</v>
+        <v>13.9</v>
       </c>
       <c r="U16" t="n">
-        <v>21.6</v>
+        <v>13.6</v>
       </c>
       <c r="V16" t="n">
-        <v>21.6</v>
+        <v>13.6</v>
       </c>
       <c r="W16" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="X16" t="n">
-        <v>20.3</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>21.4</v>
+        <v>13.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.3</v>
+        <v>13.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.8</v>
+        <v>13.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>19.9</v>
+        <v>13.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.9</v>
+        <v>13.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>20.8</v>
+        <v>13.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>19.3</v>
+        <v>13.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>20.7</v>
+        <v>13.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>20.8</v>
+        <v>13.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>19.8</v>
+        <v>13.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20.1</v>
+        <v>13.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>21.3</v>
+        <v>13.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>21.4</v>
+        <v>13.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>20</v>
+        <v>13.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>20.3</v>
+        <v>13.7</v>
       </c>
       <c r="AO16" t="n">
-        <v>21.6</v>
+        <v>13.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>21.5</v>
+        <v>13.7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20.5</v>
+        <v>14.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>20.8</v>
+        <v>14.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>22.2</v>
+        <v>14.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>22.1</v>
+        <v>14.4</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_100856.csv</t>
+          <t>hvbDatalog_2026-03-02_080850.csv</t>
         </is>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>15.39</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AX16" t="n">
-        <v>236.8521</v>
+        <v>78.85440000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>-1.390000000000001</v>
+        <v>0.0200000000000013</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0.1899999999999977</v>
+        <v>0.0099999999999909</v>
       </c>
       <c r="BA16" t="n">
-        <v>-1.390000000000001</v>
+        <v>0.0200000000000013</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0.1899999999999977</v>
+        <v>0.0099999999999909</v>
       </c>
       <c r="BC16" t="n">
-        <v>6640.6</v>
+        <v>3372.26</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0300000000000002</v>
+        <v>1</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0699999999999998</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>20.828125</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.8359789991960171</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>22.2</v>
+        <v>13.721875</v>
       </c>
       <c r="BJ16" t="n">
-        <v>19</v>
+        <v>0.4462997509991861</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.2</v>
+        <v>14.8</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0062500000000014</v>
+        <v>13.2</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>0.0062499999999996</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.0062500000000014</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>0.0062499999999996</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.2079272119605449</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.353354363004915</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0019493176121301</v>
+        <v>0.1801801801801803</v>
       </c>
       <c r="BU16" t="n">
-        <v>16.68389830508475</v>
+        <v>1.545256193693693</v>
       </c>
       <c r="BV16" t="n">
-        <v>431.3579661016949</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>20.72876059322034</v>
+        <v>8.482436974789916</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.8367576150486949</v>
+        <v>378.5815966386554</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.194915254237289</v>
+        <v>13.70926995798319</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0139830508474575</v>
+        <v>0.4399867597201848</v>
       </c>
       <c r="CA16" t="n">
+        <v>1.526890756302521</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0.0062184873949579</v>
+      </c>
+      <c r="CC16" t="n">
         <v>-1</v>
       </c>
-      <c r="CB16" t="n">
-        <v>-0.0606983444196493</v>
+      <c r="CD16" t="n">
+        <v>-0.065135366362709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02 09:49:12</t>
+          <t>2026-03-02 12:17:13</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>94</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="D17" t="n">
-        <v>8.880000000000001</v>
+        <v>16.57</v>
       </c>
       <c r="E17" t="n">
-        <v>379.76</v>
+        <v>443.18</v>
       </c>
       <c r="F17" t="n">
-        <v>3372.26</v>
+        <v>7344.31</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -4542,238 +4642,244 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>3.38</v>
+        <v>3.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>14.6</v>
+        <v>22.8</v>
       </c>
       <c r="P17" t="n">
-        <v>14.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.4</v>
+        <v>24.3</v>
       </c>
       <c r="R17" t="n">
-        <v>14.3</v>
+        <v>24.3</v>
       </c>
       <c r="S17" t="n">
-        <v>13.9</v>
+        <v>22.7</v>
       </c>
       <c r="T17" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="U17" t="n">
-        <v>13.6</v>
+        <v>24</v>
       </c>
       <c r="V17" t="n">
-        <v>13.6</v>
+        <v>24</v>
       </c>
       <c r="W17" t="n">
-        <v>13.5</v>
+        <v>22.1</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>22.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.4</v>
+        <v>23.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>13.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.4</v>
+        <v>21.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.3</v>
+        <v>22</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.2</v>
+        <v>23</v>
       </c>
       <c r="AD17" t="n">
-        <v>13.2</v>
+        <v>22.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.4</v>
+        <v>20.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.2</v>
+        <v>22.9</v>
       </c>
       <c r="AH17" t="n">
-        <v>13.3</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>13.5</v>
+        <v>21.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13.5</v>
+        <v>22.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
       </c>
       <c r="AL17" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>13.7</v>
+        <v>22.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>13.7</v>
+        <v>22.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>13.7</v>
+        <v>23.9</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.7</v>
+        <v>23.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.1</v>
+        <v>22.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.2</v>
+        <v>22.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.4</v>
+        <v>24.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.4</v>
+        <v>24.2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_080850.csv</t>
+          <t>hvbDatalog_2026-03-02_120814.csv</t>
         </is>
       </c>
       <c r="AV17" t="n">
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.880000000000001</v>
+        <v>16.57</v>
       </c>
       <c r="AX17" t="n">
-        <v>78.85440000000001</v>
+        <v>274.5649</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0200000000000013</v>
+        <v>15.31</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0099999999999909</v>
+        <v>2.259999999999991</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0200000000000013</v>
+        <v>15.31</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0099999999999909</v>
+        <v>2.259999999999991</v>
       </c>
       <c r="BC17" t="n">
-        <v>3372.26</v>
+        <v>7344.31</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>13.721875</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.4462997509991861</v>
+        <v>0.04</v>
       </c>
       <c r="BI17" t="n">
-        <v>14.8</v>
+        <v>22.925</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13.2</v>
+        <v>0.9615176176400816</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.600000000000001</v>
+        <v>24.3</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0062499999999996</v>
+        <v>20.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1000000000000014</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0062499999999996</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.1801801598896218</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.545256019678376</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>0.2293301146650573</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.482436974789916</v>
+        <v>1.383524441762221</v>
       </c>
       <c r="BV17" t="n">
-        <v>378.5815966386554</v>
+        <v>0.0018105009052504</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.70926995798319</v>
+        <v>16.97</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.4399867597201848</v>
+        <v>443.2608474576271</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.526890756302521</v>
+        <v>22.86347987288136</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0062184873949579</v>
+        <v>0.9622297379250128</v>
       </c>
       <c r="CA17" t="n">
+        <v>3.778813559322035</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0.0112711864406781</v>
+      </c>
+      <c r="CC17" t="n">
         <v>-1</v>
       </c>
-      <c r="CB17" t="n">
-        <v>-0.0604232745756098</v>
+      <c r="CD17" t="n">
+        <v>-0.0631783173966281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02 12:53:13</t>
+          <t>2026-03-02 12:47:18</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>94</v>
       </c>
       <c r="C18" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="E18" t="n">
-        <v>453.75</v>
+        <v>453</v>
       </c>
       <c r="F18" t="n">
-        <v>1.36</v>
+        <v>713.02</v>
       </c>
       <c r="G18" t="n">
         <v>25</v>
@@ -4788,40 +4894,40 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="L18" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M18" t="n">
         <v>4.03</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.04</v>
-      </c>
       <c r="N18" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="O18" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="P18" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q18" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>24</v>
+      </c>
+      <c r="U18" t="n">
         <v>24.9</v>
       </c>
-      <c r="R18" t="n">
+      <c r="V18" t="n">
         <v>24.9</v>
-      </c>
-      <c r="S18" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="V18" t="n">
-        <v>24.8</v>
       </c>
       <c r="W18" t="n">
         <v>23.1</v>
@@ -4830,10 +4936,10 @@
         <v>23.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA18" t="n">
         <v>22.7</v>
@@ -4842,58 +4948,58 @@
         <v>22.9</v>
       </c>
       <c r="AC18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD18" t="n">
         <v>23.7</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE18" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>23.4</v>
-      </c>
       <c r="AR18" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AS18" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AT18" t="n">
         <v>25</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>24.8</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -4904,125 +5010,131 @@
         <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2.4649</v>
       </c>
       <c r="AY18" t="n">
-        <v>-6.59</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-1.199999999999989</v>
+        <v>-0.08999999999997491</v>
       </c>
       <c r="BA18" t="n">
-        <v>-6.59</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-1.199999999999989</v>
+        <v>-0.08999999999997491</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.36</v>
+        <v>713.02</v>
       </c>
       <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
         <v>1</v>
       </c>
-      <c r="BE18" t="n">
-        <v>0.0199999999999995</v>
-      </c>
       <c r="BF18" t="n">
-        <v>0.0099999999999997</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>23.715625</v>
+        <v>0.0200000000000004</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.94086760749784</v>
+        <v>0.0100000000000006</v>
       </c>
       <c r="BI18" t="n">
-        <v>25</v>
+        <v>23.83125</v>
       </c>
       <c r="BJ18" t="n">
-        <v>21.1</v>
+        <v>0.9539180664078832</v>
       </c>
       <c r="BK18" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="BM18" t="n">
         <v>3.899999999999999</v>
       </c>
-      <c r="BL18" t="n">
-        <v>0.0031250000000007</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0</v>
-      </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0.0062500000000014</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.0031250000000007</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
         <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>-0.0062500000000014</v>
       </c>
       <c r="BR18" t="n">
-        <v>3899999.999999999</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>23715625</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>19999.99999999957</v>
+        <v>2.484076433121018</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.77</v>
+        <v>15.17914012738853</v>
       </c>
       <c r="BV18" t="n">
-        <v>454.8370588235294</v>
+        <v>0.012738853503185</v>
       </c>
       <c r="BW18" t="n">
-        <v>23.73568802521008</v>
+        <v>10.74661016949152</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.9479751556890356</v>
+        <v>454.7410169491525</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.850420168067227</v>
+        <v>23.84340572033898</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.0100840336134451</v>
+        <v>0.9609419817927946</v>
       </c>
       <c r="CA18" t="n">
+        <v>3.887288135593219</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0.0105084745762709</v>
+      </c>
+      <c r="CC18" t="n">
         <v>-1</v>
       </c>
-      <c r="CB18" t="n">
-        <v>-0.0591711237579624</v>
+      <c r="CD18" t="n">
+        <v>-0.0622945425019683</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02 11:53:18</t>
+          <t>2026-03-02 11:59:14</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>94</v>
       </c>
       <c r="C19" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D19" t="n">
-        <v>16.32</v>
+        <v>16.91</v>
       </c>
       <c r="E19" t="n">
-        <v>434.34</v>
+        <v>436.86</v>
       </c>
       <c r="F19" t="n">
-        <v>7086.27</v>
+        <v>7388.98</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" t="n">
         <v>19</v>
@@ -5034,112 +5146,112 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M19" t="n">
         <v>3.87</v>
       </c>
-      <c r="L19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.83</v>
-      </c>
       <c r="N19" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="O19" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="P19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T19" t="n">
         <v>21.8</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>22.7</v>
       </c>
-      <c r="R19" t="n">
+      <c r="V19" t="n">
         <v>22.7</v>
       </c>
-      <c r="S19" t="n">
+      <c r="W19" t="n">
         <v>21</v>
       </c>
-      <c r="T19" t="n">
+      <c r="X19" t="n">
         <v>21.3</v>
       </c>
-      <c r="U19" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AI19" t="n">
         <v>20.8</v>
       </c>
-      <c r="Y19" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AJ19" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AR19" t="n">
         <v>21.8</v>
       </c>
-      <c r="AA19" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>21.3</v>
-      </c>
       <c r="AS19" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -5150,374 +5262,386 @@
         <v>1</v>
       </c>
       <c r="AW19" t="n">
-        <v>16.32</v>
+        <v>16.91</v>
       </c>
       <c r="AX19" t="n">
-        <v>266.3424</v>
+        <v>285.9481</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.0100000000000015</v>
+        <v>16.91</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.0199999999999818</v>
+        <v>2.730000000000018</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.0100000000000015</v>
+        <v>16.91</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.0199999999999818</v>
+        <v>2.730000000000018</v>
       </c>
       <c r="BC19" t="n">
-        <v>7086.27</v>
+        <v>7388.98</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>21.3625</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.9050931158654872</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BI19" t="n">
-        <v>22.8</v>
+        <v>21.85625</v>
       </c>
       <c r="BJ19" t="n">
-        <v>19.3</v>
+        <v>0.9290777598624174</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.5</v>
+        <v>23.3</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.0062499999999978</v>
+        <v>19.7</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1000000000000014</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.0062499999999978</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.0031250000000007</v>
       </c>
       <c r="BR19" t="n">
-        <v>0.2144607711727468</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.308976635479373</v>
+        <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.0012254901209871</v>
+        <v>0.2128917800118274</v>
       </c>
       <c r="BU19" t="n">
-        <v>16.21428571428572</v>
+        <v>1.292504435245417</v>
       </c>
       <c r="BV19" t="n">
-        <v>433.9425210084034</v>
+        <v>0.0017740981667652</v>
       </c>
       <c r="BW19" t="n">
-        <v>21.27326680672269</v>
+        <v>16.77533898305085</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.881315374186958</v>
+        <v>436.7188983050847</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.384033613445378</v>
+        <v>21.77558262711865</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.0160504201680672</v>
+        <v>0.9128639085117526</v>
       </c>
       <c r="CA19" t="n">
+        <v>3.51864406779661</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0.0118644067796612</v>
+      </c>
+      <c r="CC19" t="n">
         <v>-1</v>
       </c>
-      <c r="CB19" t="n">
-        <v>-0.0586514134032478</v>
+      <c r="CD19" t="n">
+        <v>-0.0619094026373482</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02 11:47:13</t>
+          <t>2026-03-02 21:55:41</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>94</v>
       </c>
       <c r="C20" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>-0</v>
+        <v>-15.68</v>
       </c>
       <c r="E20" t="n">
-        <v>428.56</v>
+        <v>385.66</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.29</v>
+        <v>-6046.33</v>
       </c>
       <c r="G20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H20" t="n">
+        <v>17</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AC20" t="n">
         <v>18</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="O20" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20</v>
-      </c>
-      <c r="X20" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>20.9</v>
-      </c>
       <c r="AD20" t="n">
-        <v>20.7</v>
+        <v>17.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF20" t="n">
-        <v>19.3</v>
+        <v>17.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>20.7</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="AI20" t="n">
-        <v>19.8</v>
+        <v>17.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20.1</v>
+        <v>17.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>21.3</v>
+        <v>18.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>21.4</v>
+        <v>18.3</v>
       </c>
       <c r="AM20" t="n">
-        <v>20</v>
+        <v>17.7</v>
       </c>
       <c r="AN20" t="n">
-        <v>20.3</v>
+        <v>17.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>21.6</v>
+        <v>18.7</v>
       </c>
       <c r="AP20" t="n">
-        <v>21.5</v>
+        <v>18.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>20.5</v>
+        <v>18</v>
       </c>
       <c r="AR20" t="n">
-        <v>20.8</v>
+        <v>18.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>22.2</v>
+        <v>19.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>22.1</v>
+        <v>19.1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_100856.csv</t>
+          <t>hvbDatalog_2026-03-02_200953.csv</t>
         </is>
       </c>
       <c r="AV20" t="n">
         <v>1</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>245.8624</v>
       </c>
       <c r="AY20" t="n">
-        <v>-16.8</v>
+        <v>-0.0299999999999993</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-3.240000000000009</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-16.8</v>
+        <v>-0.0299999999999993</v>
       </c>
       <c r="BB20" t="n">
-        <v>-3.240000000000009</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.29</v>
+        <v>6046.33</v>
       </c>
       <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1</v>
       </c>
-      <c r="BE20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0.06</v>
-      </c>
       <c r="BG20" t="n">
-        <v>20.81875</v>
+        <v>0.0300000000000002</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.8360573757128582</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="BI20" t="n">
-        <v>22.2</v>
+        <v>18.140625</v>
       </c>
       <c r="BJ20" t="n">
-        <v>19</v>
+        <v>0.6036765717052525</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.2</v>
+        <v>19.2</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0.0031249999999971</v>
+        <v>17</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>0.0031249999999971</v>
       </c>
       <c r="BO20" t="n">
-        <v>-0.0031249999999971</v>
+        <v>0.0999999999999978</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>0.0999999999999978</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>0.0031249999999971</v>
       </c>
       <c r="BR20" t="n">
-        <v>3200000</v>
+        <v>0.0999999999999978</v>
       </c>
       <c r="BS20" t="n">
-        <v>20818750</v>
+        <v>0.0999999999999978</v>
       </c>
       <c r="BT20" t="n">
-        <v>20000.00000000002</v>
+        <v>0.1403061224489795</v>
       </c>
       <c r="BU20" t="n">
-        <v>16.69881355932203</v>
+        <v>1.156927614795918</v>
       </c>
       <c r="BV20" t="n">
-        <v>431.3483898305085</v>
+        <v>0.0019132653061224</v>
       </c>
       <c r="BW20" t="n">
-        <v>20.72547669491526</v>
+        <v>-15.51415254237288</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.8366455963751783</v>
+        <v>386.2372033898305</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.194915254237289</v>
+        <v>18.08538135593221</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.01364406779661</v>
+        <v>0.5897517516983479</v>
       </c>
       <c r="CA20" t="n">
+        <v>2.129661016949154</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>0.0225423728813559</v>
+      </c>
+      <c r="CC20" t="n">
         <v>-1</v>
       </c>
-      <c r="CB20" t="n">
-        <v>-0.0580724268158241</v>
+      <c r="CD20" t="n">
+        <v>-0.0611266178799556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02 21:55:41</t>
+          <t>2026-03-02 12:17:15</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>94</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>-15.68</v>
+        <v>16.19</v>
       </c>
       <c r="E21" t="n">
-        <v>385.66</v>
+        <v>443.31</v>
       </c>
       <c r="F21" t="n">
-        <v>-6046.33</v>
+        <v>7175.33</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -5526,216 +5650,222 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>3.89</v>
       </c>
       <c r="O21" t="n">
-        <v>18.6</v>
+        <v>22.8</v>
       </c>
       <c r="P21" t="n">
-        <v>18.9</v>
+        <v>23.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>19.2</v>
+        <v>24.3</v>
       </c>
       <c r="R21" t="n">
-        <v>19.1</v>
+        <v>24.3</v>
       </c>
       <c r="S21" t="n">
-        <v>18.1</v>
+        <v>22.7</v>
       </c>
       <c r="T21" t="n">
-        <v>18.2</v>
+        <v>23</v>
       </c>
       <c r="U21" t="n">
-        <v>18.7</v>
+        <v>24</v>
       </c>
       <c r="V21" t="n">
-        <v>18.7</v>
+        <v>24</v>
       </c>
       <c r="W21" t="n">
-        <v>17.5</v>
+        <v>22.1</v>
       </c>
       <c r="X21" t="n">
-        <v>17.7</v>
+        <v>22.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.2</v>
+        <v>23.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.1</v>
+        <v>23.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>17.3</v>
+        <v>21.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>17.4</v>
+        <v>22</v>
       </c>
       <c r="AC21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.9</v>
+        <v>22.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>17.2</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.1</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>17.4</v>
+        <v>21.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17.5</v>
+        <v>22.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.2</v>
+        <v>23.4</v>
       </c>
       <c r="AL21" t="n">
-        <v>18.3</v>
+        <v>23.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>17.7</v>
+        <v>22.1</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.8</v>
+        <v>22.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>18.7</v>
+        <v>23.9</v>
       </c>
       <c r="AP21" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>22.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.2</v>
+        <v>22.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>19.1</v>
+        <v>24.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>19.1</v>
+        <v>24.2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>hvbDatalog_2026-03-02_200953.csv</t>
+          <t>hvbDatalog_2026-03-02_120814.csv</t>
         </is>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>15.68</v>
+        <v>16.19</v>
       </c>
       <c r="AX21" t="n">
-        <v>245.8624</v>
+        <v>262.1161</v>
       </c>
       <c r="AY21" t="n">
-        <v>-0.0299999999999993</v>
+        <v>0.9500000000000012</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.1999999999999886</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.0299999999999993</v>
+        <v>0.9500000000000012</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>0.1999999999999886</v>
       </c>
       <c r="BC21" t="n">
-        <v>6046.33</v>
+        <v>7175.33</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
         <v>0.0300000000000002</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BH21" t="n">
         <v>0.0299999999999998</v>
       </c>
-      <c r="BG21" t="n">
-        <v>18.140625</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0.6036765717052525</v>
-      </c>
       <c r="BI21" t="n">
-        <v>19.2</v>
+        <v>22.93125</v>
       </c>
       <c r="BJ21" t="n">
-        <v>17</v>
+        <v>0.954932019198394</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.2</v>
+        <v>24.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.0031249999999971</v>
+        <v>20.5</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.0999999999999978</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>0.0999999999999978</v>
+        <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.0031249999999971</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>0.0999999999999978</v>
+        <v>0</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0.0999999999999978</v>
+        <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>0.1403061135008856</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.156927541012274</v>
+        <v>0</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.001913265184103</v>
+        <v>0.2347127856701668</v>
       </c>
       <c r="BU21" t="n">
-        <v>-15.51415254237288</v>
+        <v>1.416383570105003</v>
       </c>
       <c r="BV21" t="n">
-        <v>386.2372033898305</v>
+        <v>0.0018529956763434</v>
       </c>
       <c r="BW21" t="n">
-        <v>18.08538135593221</v>
+        <v>16.94127118644068</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.5897517516983479</v>
+        <v>443.2641525423729</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.129661016949154</v>
+        <v>22.86546610169491</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.0225423728813559</v>
+        <v>0.9621355903914768</v>
       </c>
       <c r="CA21" t="n">
+        <v>3.778813559322034</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>0.01135593220339</v>
+      </c>
+      <c r="CC21" t="n">
         <v>-1</v>
       </c>
-      <c r="CB21" t="n">
-        <v>-0.0579947445869679</v>
+      <c r="CD21" t="n">
+        <v>-0.0592271482478256</v>
       </c>
     </row>
   </sheetData>
